--- a/deliverables/2026_산자부_연구비집행계획_D2O_1차년도.xlsx
+++ b/deliverables/2026_산자부_연구비집행계획_D2O_1차년도.xlsx
@@ -1616,9 +1616,12 @@
         <is>
           <t>연구활동비 잔액 8,721.555천원(편성 9,000 − 기집행 278.445)
 · 국내여비(주관기관 GMW·충남대 협의, 실증현장 출장) 1,000천원(11월), 1,721.555천원(12월)
-· 회의비(실증 준비·1차년도 점검 회의) 1,000천원(11월), 1,000천원(12월)
+· 외부 전문가 자문회의(산·학·관 전문가 6인 초청, 2회 — 실증 설계 검증·요구사항 정의서 자문) 1,000천원(11월), 1,000천원(12월)
+   - 자문 수당 250천원×3인 = 750천원/회 (기타소득 원천징수 후 계좌 지급)
+   - 회의 식비·다과 250천원/회 (외부 3인 + 내부 참석 3인)
 · 사무실운영비(실증 기록·사무 소모품) 500천원(11월), 500천원(12월)
-· 우편요금(시료·자료 발송) 500천원(11월), 500천원(12월)
+· 야근·특근 식대(참여연구원, 저녁 2회차 교반·실증 기록) 300천원(11월), 300천원(12월)
+· 우편요금(시료·자료 발송) 200천원(11월), 200천원(12월)
 · 문헌구입비(깔개관리·악취저감 관련 문헌) 1,000천원(11월)
 · 국외여비(해외 깔개관리·축산로봇 기술동향 조사) 1,000천원(12월)</t>
         </is>
@@ -1777,7 +1780,7 @@
           <t>※ 11월~이듬해 봄 축사 베딩 정비기에 맞춰 실증 축사(송영신목장) 깔개 구축
 · 피트모스 구매대금 지급 11,164천원(11월 1주) — 1,116.4천원×10
 · 깔짚 구매대금 지급 11,000천원(11월 1주) — 1,100천원×10
-· 연료비(장비운행): 대동 트랙터 1일 1회(약 30분) 깔개 교반작업 연료 및 트랙터 정비비 5,000천원(11월), 5,000천원(12월) — 수동 교반 대조군(자율주행 로봇 비교 기준) 데이터 확보</t>
+· 연료비(장비운행): 56HP 트랙터 1일 2회(아침·저녁, 회당 약 30분) 휴식공간 1,368㎡ 깔개 교반작업 연료 및 트랙터 정비비 5,000천원(11월), 5,000천원(12월) — 수동 교반 대조군(자율주행 로봇 비교 기준선) 데이터 확보, 마스터 연구노트 No.2 SOP-M1 기준</t>
         </is>
       </c>
       <c r="E41" s="67" t="n">

--- a/deliverables/2026_산자부_연구비집행계획_D2O_1차년도.xlsx
+++ b/deliverables/2026_산자부_연구비집행계획_D2O_1차년도.xlsx
@@ -1614,16 +1614,16 @@
       </c>
       <c r="D36" s="69" t="inlineStr">
         <is>
-          <t>연구활동비 잔액 8,721.555천원(편성 9,000 − 기집행 278.445)
-· 국내여비(주관기관 GMW·충남대 협의, 실증현장 출장) 1,000천원(11월), 1,721.555천원(12월)
-· 외부 전문가 자문회의(산·학·관 전문가 6인 초청, 2회 — 실증 설계 검증·요구사항 정의서 자문) 1,000천원(11월), 1,000천원(12월)
-   - 자문 수당 250천원×3인 = 750천원/회 (기타소득 원천징수 후 계좌 지급)
-   - 회의 식비·다과 250천원/회 (외부 3인 + 내부 참석 3인)
-· 사무실운영비(실증 기록·사무 소모품) 500천원(11월), 500천원(12월)
-· 야근·특근 식대(참여연구원, 저녁 2회차 교반·실증 기록) 300천원(11월), 300천원(12월)
-· 우편요금(시료·자료 발송) 200천원(11월), 200천원(12월)
-· 문헌구입비(깔개관리·악취저감 관련 문헌) 1,000천원(11월)
-· 국외여비(해외 깔개관리·축산로봇 기술동향 조사) 1,000천원(12월)</t>
+          <t>· 회의비: 외부 전문가 자문회의(산·학·관 전문가 6인 초청) 1차 1,000천원(11월 초), 2차 1,000천원(12월 초)
+   - 1차: 갈전구리 실증 설계·HBP 운영 기준 검증 / 2차: 수동 교반 기준선 데이터·실증지 요구사항 검토
+   - 회당 전문가 자문수당 3인 및 회의 식비·다과
+· 국내여비: 주관기관(GMW)·충남대 실증 협의 및 현장 출장 1,300천원(11월), 1,421.555천원(12월)
+· 사무실운영비: 실증 기록·사무 소모품 500천원(11월), 500천원(12월)
+· 야근·특근 식대: 참여연구원 저녁 2회차 교반·실증 기록 300천원(11월), 300천원(12월)
+· 우편요금: 자료·시료 발송 200천원(11월), 200천원(12월)
+· 문헌구입비: CBP·깔개관리·악취저감 관련 문헌 1,000천원(11월)
+· 국외여비: 해외 CBP 우사·깔개관리 기술동향 조사 1,000천원(12월)
+※ 연구활동비 전액 12월 말까지 집행 완료</t>
         </is>
       </c>
       <c r="E36" s="65" t="n">
@@ -1636,11 +1636,11 @@
         <v>8721.555</v>
       </c>
       <c r="H36" s="55">
-        <f>F36/E36</f>
+        <f>IF(E36=0,"-",F36/E36)</f>
         <v/>
       </c>
       <c r="I36" s="55">
-        <f>(F36+G36)/E36</f>
+        <f>IF(E36=0,"-",(F36+G36)/E36)</f>
         <v/>
       </c>
     </row>
@@ -1653,8 +1653,9 @@
       </c>
       <c r="D37" s="69" t="inlineStr">
         <is>
-          <t>참여연구원 연구수당 지급 1,463천원(12월)
-(1차년도 연구성과 기여도 평가 후 지급)</t>
+          <t>· 연구수당: 참여연구원 연구수당 1,463천원(12월)
+   - 1차년도 연구성과 기여도 평가 후 지급
+※ 12월 말까지 집행 완료</t>
         </is>
       </c>
       <c r="E37" s="65" t="n">
@@ -1667,11 +1668,11 @@
         <v>1463</v>
       </c>
       <c r="H37" s="55">
-        <f>F37/E37</f>
+        <f>IF(E37=0,"-",F37/E37)</f>
         <v/>
       </c>
       <c r="I37" s="55">
-        <f>(F37+G37)/E37</f>
+        <f>IF(E37=0,"-",(F37+G37)/E37)</f>
         <v/>
       </c>
     </row>
@@ -1684,10 +1685,9 @@
       </c>
       <c r="D38" s="69" t="inlineStr">
         <is>
-          <t>신규 참여연구원(과장) 인건비(현금분) 지급
-· 10월분 1,306천원(10월)
-· 11월분 1,306천원(11월)
-· 12월분 1,306천원(12월)</t>
+          <t>· 인건비: 신규 참여연구원(과장, 참여율 100%) 인건비 현금분
+   - 10월분 1,306천원(10월), 11월분 1,306천원(11월), 12월분 1,306천원(12월)
+※ 12월 말까지 집행 완료</t>
         </is>
       </c>
       <c r="E38" s="67" t="n">
@@ -1700,11 +1700,11 @@
         <v>3918</v>
       </c>
       <c r="H38" s="55">
-        <f>F38/E38</f>
+        <f>IF(E38=0,"-",F38/E38)</f>
         <v/>
       </c>
       <c r="I38" s="55">
-        <f>(F38+G38)/E38</f>
+        <f>IF(E38=0,"-",(F38+G38)/E38)</f>
         <v/>
       </c>
     </row>
@@ -1730,11 +1730,11 @@
         <v>0</v>
       </c>
       <c r="H39" s="55">
-        <f>F39/E39</f>
+        <f>IF(E39=0,"-",F39/E39)</f>
         <v/>
       </c>
       <c r="I39" s="55">
-        <f>(F39+G39)/E39</f>
+        <f>IF(E39=0,"-",(F39+G39)/E39)</f>
         <v/>
       </c>
     </row>
@@ -1760,11 +1760,11 @@
         <v>0</v>
       </c>
       <c r="H40" s="55">
-        <f>F40/E40</f>
+        <f>IF(E40=0,"-",F40/E40)</f>
         <v/>
       </c>
       <c r="I40" s="55">
-        <f>(F40+G40)/E40</f>
+        <f>IF(E40=0,"-",(F40+G40)/E40)</f>
         <v/>
       </c>
     </row>
@@ -1777,10 +1777,10 @@
       </c>
       <c r="D41" s="69" t="inlineStr">
         <is>
-          <t>※ 11월~이듬해 봄 축사 베딩 정비기에 맞춰 실증 축사(송영신목장) 깔개 구축
-· 피트모스 구매대금 지급 11,164천원(11월 1주) — 1,116.4천원×10
-· 깔짚 구매대금 지급 11,000천원(11월 1주) — 1,100천원×10
-· 연료비(장비운행): 56HP 트랙터 1일 2회(아침·저녁, 회당 약 30분) 휴식공간 1,368㎡ 깔개 교반작업 연료 및 트랙터 정비비 5,000천원(11월), 5,000천원(12월) — 수동 교반 대조군(자율주행 로봇 비교 기준선) 데이터 확보, 마스터 연구노트 No.2 SOP-M1 기준</t>
+          <t>· 피트모스 구매: 11,164천원(11월 초 구입) — 1,116.4천원 × 10
+· 깔짚(톱밥) 구매: 11,000천원(11월 초 구입) — 1,100천원 × 10
+   - 실증 우사(송영신목장) 겨울철~봄철 HBP 침상 준비용 (11월 초 일괄 구입·입고 후 침상 보충에 순차 투입)
+· 연료비(장비운행): 트랙터 1일 2회 수동 교반(갈전구리 비교 기준선 확보) 5,000천원(11월), 5,000천원(12월) — 500천원 × 20회, 12월 말까지 집행 완료</t>
         </is>
       </c>
       <c r="E41" s="67" t="n">
@@ -1793,11 +1793,11 @@
         <v>32164</v>
       </c>
       <c r="H41" s="55">
-        <f>F41/E41</f>
+        <f>IF(E41=0,"-",F41/E41)</f>
         <v/>
       </c>
       <c r="I41" s="55">
-        <f>(F41+G41)/E41</f>
+        <f>IF(E41=0,"-",(F41+G41)/E41)</f>
         <v/>
       </c>
     </row>
@@ -1823,11 +1823,11 @@
         <v>0</v>
       </c>
       <c r="H42" s="55">
-        <f>F42/E42</f>
+        <f>IF(E42=0,"-",F42/E42)</f>
         <v/>
       </c>
       <c r="I42" s="55">
-        <f>(F42+G42)/E42</f>
+        <f>IF(E42=0,"-",(F42+G42)/E42)</f>
         <v/>
       </c>
     </row>
@@ -1844,7 +1844,8 @@
       </c>
       <c r="D43" s="69" t="inlineStr">
         <is>
-          <t>지식재산권(특허) 출원 비용 2,000천원(12월)</t>
+          <t>· 지식재산권 출원: 실증 성과 관련 특허 출원 비용 2,000천원(12월)
+※ 12월 말까지 집행 완료</t>
         </is>
       </c>
       <c r="E43" s="65" t="n">
@@ -1857,11 +1858,11 @@
         <v>2000</v>
       </c>
       <c r="H43" s="55">
-        <f>F43/E43</f>
+        <f>IF(E43=0,"-",F43/E43)</f>
         <v/>
       </c>
       <c r="I43" s="55">
-        <f>(F43+G43)/E43</f>
+        <f>IF(E43=0,"-",(F43+G43)/E43)</f>
         <v/>
       </c>
     </row>

--- a/deliverables/2026_산자부_연구비집행계획_D2O_1차년도.xlsx
+++ b/deliverables/2026_산자부_연구비집행계획_D2O_1차년도.xlsx
@@ -1617,12 +1617,15 @@
           <t>· 회의비: 외부 전문가 자문회의(산·학·관 전문가 6인 초청) 1차 1,000천원(11월 초), 2차 1,000천원(12월 초)
    - 1차: 갈전구리 실증 설계·HBP 운영 기준 검증 / 2차: 수동 교반 기준선 데이터·실증지 요구사항 검토
    - 회당 전문가 자문수당 3인 및 회의 식비·다과
-· 국내여비: 주관기관(GMW)·충남대 실증 협의 및 현장 출장 1,300천원(11월), 1,421.555천원(12월)
+· 국내여비 3,721.555천원
+   - 주관기관(GMW)·충남대 실증 협의 및 현장 출장 1,000천원(11월), 1,000천원(12월)
+   - 국내 깔짚(CBP형) 우사 실증 비교 현장조사 500천원(11월), 500천원(12월)
+   - 지자체·농협·축협 대상 HBP·갈전구리 실증 소개(확산 기반 구축) 721.555천원(12월)
 · 사무실운영비: 실증 기록·사무 소모품 500천원(11월), 500천원(12월)
-· 야근·특근 식대: 참여연구원 저녁 2회차 교반·실증 기록 300천원(11월), 300천원(12월)
+· 야근·특근 식대: 참여연구원 저녁 2회차 교반·실증 기록(초과근무 기록 확인분) 300천원(11월), 300천원(12월)
 · 우편요금: 자료·시료 발송 200천원(11월), 200천원(12월)
 · 문헌구입비: CBP·깔개관리·악취저감 관련 문헌 1,000천원(11월)
-· 국외여비: 해외 CBP 우사·깔개관리 기술동향 조사 1,000천원(12월)
+※ 국외여비(해외 전시회 참관) 1,000천원은 일정 취소로 국내여비로 전환
 ※ 연구활동비 전액 12월 말까지 집행 완료</t>
         </is>
       </c>

--- a/deliverables/2026_산자부_연구비집행계획_D2O_1차년도.xlsx
+++ b/deliverables/2026_산자부_연구비집행계획_D2O_1차년도.xlsx
@@ -1783,7 +1783,10 @@
           <t>· 피트모스 구매: 11,164천원(11월 초 구입) — 1,116.4천원 × 10
 · 깔짚(톱밥) 구매: 11,000천원(11월 초 구입) — 1,100천원 × 10
    - 실증 우사(송영신목장) 겨울철~봄철 HBP 침상 준비용 (11월 초 일괄 구입·입고 후 침상 보충에 순차 투입)
-· 연료비(장비운행): 트랙터 1일 2회 수동 교반(갈전구리 비교 기준선 확보) 5,000천원(11월), 5,000천원(12월) — 500천원 × 20회, 12월 말까지 집행 완료</t>
+· 장비운행비 10,000천원 (12월 말까지 집행 완료)
+   - 연료비: 트랙터 1일 2회 수동 교반(갈전구리 비교 기준선) 주유 1,000천원(11월), 1,000천원(12월)
+   - 교반 장비 정비·수리비: 실증 교반용 트랙터·로터리 정비(로터리 날·베어링 교체, 오일·필터, 유압 점검 등) 2,000천원(11월), 1,500천원(12월)
+   - 실증 측정장비 구입: HBP 침상·우사 환경 측정용 4,500천원(11월 초) — 휴대용 암모니아 측정기, 침상 수분계, 탐침 온도계, pH 측정기, 온습도 데이터로거, 거리·깊이 측정 도구, 교정액·소모품</t>
         </is>
       </c>
       <c r="E41" s="67" t="n">

--- a/deliverables/2026_산자부_연구비집행계획_D2O_1차년도.xlsx
+++ b/deliverables/2026_산자부_연구비집행계획_D2O_1차년도.xlsx
@@ -16,12 +16,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="167" formatCode="#,##0.###"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <name val="맑은 고딕"/>
       <charset val="129"/>
@@ -171,6 +172,11 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="FF000000"/>
+      <sz val="14"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -345,7 +351,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -593,6 +599,32 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -904,14 +936,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:I44"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.625" defaultRowHeight="16.5"/>
   <cols>
     <col width="9" customWidth="1" style="50" min="2" max="2"/>
     <col width="15.5" bestFit="1" customWidth="1" style="50" min="3" max="3"/>
-    <col width="53.75" customWidth="1" style="50" min="4" max="4"/>
+    <col width="78" customWidth="1" style="50" min="4" max="4"/>
     <col width="17" customWidth="1" style="50" min="5" max="5"/>
     <col width="17.125" customWidth="1" style="50" min="6" max="6"/>
     <col width="17.125" customWidth="1" style="1" min="7" max="7"/>
@@ -953,9 +985,9 @@
           <t>과제명:</t>
         </is>
       </c>
-      <c r="C5" s="33" t="inlineStr">
-        <is>
-          <t>과제명 작성</t>
+      <c r="C5" s="83" t="inlineStr">
+        <is>
+          <t>축사 환경 개선을 위한 자율주행 깔개 관리 축산 로봇 개발 및 사업화 (RS-2026-25508014)</t>
         </is>
       </c>
       <c r="D5" s="40" t="n"/>
@@ -978,7 +1010,7 @@
     <row r="7" ht="20.25" customHeight="1" s="50">
       <c r="B7" s="39" t="inlineStr">
         <is>
-          <t>1. 주관연구개발기관명</t>
+          <t>1. 주관연구개발기관명: ㈜지엠더블유(GMW)</t>
         </is>
       </c>
     </row>
@@ -989,11 +1021,7 @@
         </is>
       </c>
       <c r="C8" s="51" t="n"/>
-      <c r="D8" s="37" t="inlineStr">
-        <is>
-          <t>○,○○○,○○○천원</t>
-        </is>
-      </c>
+      <c r="D8" s="37" t="n"/>
       <c r="E8" s="52" t="n"/>
       <c r="F8" s="52" t="n"/>
       <c r="I8" s="15" t="inlineStr">
@@ -1055,20 +1083,16 @@
           <t>연구활동비</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
-        <is>
-          <t>사용목적+금액(집행월) 양식으로 작성</t>
-        </is>
-      </c>
+      <c r="D10" s="20" t="n"/>
       <c r="E10" s="53" t="n"/>
       <c r="F10" s="53" t="n"/>
       <c r="G10" s="54" t="n"/>
       <c r="H10" s="55">
-        <f>F10/E10</f>
+        <f>IF(N(E10)=0,"",F10/E10)</f>
         <v/>
       </c>
       <c r="I10" s="55">
-        <f>(F10+G10)/E10</f>
+        <f>IF(N(E10)=0,"",(F10+G10)/E10)</f>
         <v/>
       </c>
     </row>
@@ -1084,43 +1108,31 @@
       <c r="F11" s="53" t="n"/>
       <c r="G11" s="54" t="n"/>
       <c r="H11" s="55">
-        <f>F11/E11</f>
+        <f>IF(N(E11)=0,"",F11/E11)</f>
         <v/>
       </c>
       <c r="I11" s="55">
-        <f>(F11+G11)/E11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="49.5" customHeight="1" s="50">
+        <f>IF(N(E11)=0,"",(F11+G11)/E11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12" s="50">
       <c r="B12" s="56" t="n"/>
       <c r="C12" s="48" t="inlineStr">
         <is>
           <t>인건비</t>
         </is>
       </c>
-      <c r="D12" s="24" t="inlineStr">
-        <is>
-          <t>(예) 
-A기업 11월분 인건비 지급 7,000천원(11월)
-A기업 12월분 인건비 지급 7,000천원(12월)</t>
-        </is>
-      </c>
-      <c r="E12" s="57" t="n">
-        <v>20000</v>
-      </c>
-      <c r="F12" s="57" t="n">
-        <v>6000</v>
-      </c>
-      <c r="G12" s="58" t="n">
-        <v>14000</v>
-      </c>
+      <c r="D12" s="24" t="n"/>
+      <c r="E12" s="57" t="n"/>
+      <c r="F12" s="57" t="n"/>
+      <c r="G12" s="58" t="n"/>
       <c r="H12" s="55">
-        <f>F12/E12</f>
+        <f>IF(N(E12)=0,"",F12/E12)</f>
         <v/>
       </c>
       <c r="I12" s="55">
-        <f>(F12+G12)/E12</f>
+        <f>IF(N(E12)=0,"",(F12+G12)/E12)</f>
         <v/>
       </c>
     </row>
@@ -1136,11 +1148,11 @@
       <c r="F13" s="53" t="n"/>
       <c r="G13" s="54" t="n"/>
       <c r="H13" s="55">
-        <f>F13/E13</f>
+        <f>IF(N(E13)=0,"",F13/E13)</f>
         <v/>
       </c>
       <c r="I13" s="55">
-        <f>(F13+G13)/E13</f>
+        <f>IF(N(E13)=0,"",(F13+G13)/E13)</f>
         <v/>
       </c>
     </row>
@@ -1156,43 +1168,31 @@
       <c r="F14" s="53" t="n"/>
       <c r="G14" s="54" t="n"/>
       <c r="H14" s="55">
-        <f>F14/E14</f>
+        <f>IF(N(E14)=0,"",F14/E14)</f>
         <v/>
       </c>
       <c r="I14" s="55">
-        <f>(F14+G14)/E14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="49.5" customHeight="1" s="50">
+        <f>IF(N(E14)=0,"",(F14+G14)/E14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" s="50">
       <c r="B15" s="56" t="n"/>
       <c r="C15" s="48" t="inlineStr">
         <is>
           <t>연구재료비</t>
         </is>
       </c>
-      <c r="D15" s="24" t="inlineStr">
-        <is>
-          <t>(예) 
-A부품 구매대금 지급 1,000천원(10월)
-B부품 구매대금 지급 25,000천원(12월)</t>
-        </is>
-      </c>
-      <c r="E15" s="57" t="n">
-        <v>50000</v>
-      </c>
-      <c r="F15" s="57" t="n">
-        <v>34900</v>
-      </c>
-      <c r="G15" s="58" t="n">
-        <v>15100</v>
-      </c>
+      <c r="D15" s="24" t="n"/>
+      <c r="E15" s="57" t="n"/>
+      <c r="F15" s="57" t="n"/>
+      <c r="G15" s="58" t="n"/>
       <c r="H15" s="55">
-        <f>F15/E15</f>
+        <f>IF(N(E15)=0,"",F15/E15)</f>
         <v/>
       </c>
       <c r="I15" s="55">
-        <f>(F15+G15)/E15</f>
+        <f>IF(N(E15)=0,"",(F15+G15)/E15)</f>
         <v/>
       </c>
     </row>
@@ -1208,11 +1208,11 @@
       <c r="F16" s="53" t="n"/>
       <c r="G16" s="54" t="n"/>
       <c r="H16" s="55">
-        <f>F16/E16</f>
+        <f>IF(N(E16)=0,"",F16/E16)</f>
         <v/>
       </c>
       <c r="I16" s="55">
-        <f>(F16+G16)/E16</f>
+        <f>IF(N(E16)=0,"",(F16+G16)/E16)</f>
         <v/>
       </c>
     </row>
@@ -1232,11 +1232,11 @@
       <c r="F17" s="53" t="n"/>
       <c r="G17" s="54" t="n"/>
       <c r="H17" s="55">
-        <f>F17/E17</f>
+        <f>IF(N(E17)=0,"",F17/E17)</f>
         <v/>
       </c>
       <c r="I17" s="55">
-        <f>(F17+G17)/E17</f>
+        <f>IF(N(E17)=0,"",(F17+G17)/E17)</f>
         <v/>
       </c>
     </row>
@@ -1261,18 +1261,18 @@
         <v/>
       </c>
       <c r="H18" s="64">
-        <f>F18/E18</f>
+        <f>IF(N(E18)=0,"",F18/E18)</f>
         <v/>
       </c>
       <c r="I18" s="64">
-        <f>(H18+G18)/F18</f>
+        <f>IF(N(E18)=0,"",(F18+G18)/E18)</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="20.25" customHeight="1" s="50">
       <c r="B20" s="39" t="inlineStr">
         <is>
-          <t>2. 공동연구개발기관명</t>
+          <t>2. 공동연구개발기관명: 충남대학교 산학협력단</t>
         </is>
       </c>
     </row>
@@ -1350,11 +1350,11 @@
       <c r="F23" s="65" t="n"/>
       <c r="G23" s="66" t="n"/>
       <c r="H23" s="55">
-        <f>F23/E23</f>
+        <f>IF(N(E23)=0,"",F23/E23)</f>
         <v/>
       </c>
       <c r="I23" s="55">
-        <f>(F23+G23)/E23</f>
+        <f>IF(N(E23)=0,"",(F23+G23)/E23)</f>
         <v/>
       </c>
     </row>
@@ -1370,11 +1370,11 @@
       <c r="F24" s="65" t="n"/>
       <c r="G24" s="66" t="n"/>
       <c r="H24" s="55">
-        <f>F24/E24</f>
+        <f>IF(N(E24)=0,"",F24/E24)</f>
         <v/>
       </c>
       <c r="I24" s="55">
-        <f>(F24+G24)/E24</f>
+        <f>IF(N(E24)=0,"",(F24+G24)/E24)</f>
         <v/>
       </c>
     </row>
@@ -1390,11 +1390,11 @@
       <c r="F25" s="67" t="n"/>
       <c r="G25" s="66" t="n"/>
       <c r="H25" s="55">
-        <f>F25/E25</f>
+        <f>IF(N(E25)=0,"",F25/E25)</f>
         <v/>
       </c>
       <c r="I25" s="55">
-        <f>(F25+G25)/E25</f>
+        <f>IF(N(E25)=0,"",(F25+G25)/E25)</f>
         <v/>
       </c>
     </row>
@@ -1410,11 +1410,11 @@
       <c r="F26" s="65" t="n"/>
       <c r="G26" s="66" t="n"/>
       <c r="H26" s="55">
-        <f>F26/E26</f>
+        <f>IF(N(E26)=0,"",F26/E26)</f>
         <v/>
       </c>
       <c r="I26" s="55">
-        <f>(F26+G26)/E26</f>
+        <f>IF(N(E26)=0,"",(F26+G26)/E26)</f>
         <v/>
       </c>
     </row>
@@ -1430,11 +1430,11 @@
       <c r="F27" s="65" t="n"/>
       <c r="G27" s="66" t="n"/>
       <c r="H27" s="55">
-        <f>F27/E27</f>
+        <f>IF(N(E27)=0,"",F27/E27)</f>
         <v/>
       </c>
       <c r="I27" s="55">
-        <f>(F27+G27)/E27</f>
+        <f>IF(N(E27)=0,"",(F27+G27)/E27)</f>
         <v/>
       </c>
     </row>
@@ -1450,11 +1450,11 @@
       <c r="F28" s="67" t="n"/>
       <c r="G28" s="66" t="n"/>
       <c r="H28" s="55">
-        <f>F28/E28</f>
+        <f>IF(N(E28)=0,"",F28/E28)</f>
         <v/>
       </c>
       <c r="I28" s="55">
-        <f>(F28+G28)/E28</f>
+        <f>IF(N(E28)=0,"",(F28+G28)/E28)</f>
         <v/>
       </c>
     </row>
@@ -1470,11 +1470,11 @@
       <c r="F29" s="65" t="n"/>
       <c r="G29" s="66" t="n"/>
       <c r="H29" s="55">
-        <f>F29/E29</f>
+        <f>IF(N(E29)=0,"",F29/E29)</f>
         <v/>
       </c>
       <c r="I29" s="55">
-        <f>(F29+G29)/E29</f>
+        <f>IF(N(E29)=0,"",(F29+G29)/E29)</f>
         <v/>
       </c>
     </row>
@@ -1494,11 +1494,11 @@
       <c r="F30" s="65" t="n"/>
       <c r="G30" s="66" t="n"/>
       <c r="H30" s="55">
-        <f>F30/E30</f>
+        <f>IF(N(E30)=0,"",F30/E30)</f>
         <v/>
       </c>
       <c r="I30" s="55">
-        <f>(F30+G30)/E30</f>
+        <f>IF(N(E30)=0,"",(F30+G30)/E30)</f>
         <v/>
       </c>
     </row>
@@ -1523,11 +1523,11 @@
         <v/>
       </c>
       <c r="H31" s="64">
-        <f>F31/E31</f>
+        <f>IF(N(E31)=0,"",F31/E31)</f>
         <v/>
       </c>
       <c r="I31" s="64">
-        <f>(F31+G31)/E31</f>
+        <f>IF(N(E31)=0,"",(F31+G31)/E31)</f>
         <v/>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="150" customHeight="1" s="50">
+    <row r="36" ht="267" customHeight="1" s="50">
       <c r="B36" s="48" t="inlineStr">
         <is>
           <t>직접비</t>
@@ -1629,13 +1629,13 @@
 ※ 연구활동비 전액 12월 말까지 집행 완료</t>
         </is>
       </c>
-      <c r="E36" s="65" t="n">
+      <c r="E36" s="78" t="n">
         <v>9000</v>
       </c>
-      <c r="F36" s="65" t="n">
+      <c r="F36" s="78" t="n">
         <v>278.445</v>
       </c>
-      <c r="G36" s="66" t="n">
+      <c r="G36" s="79" t="n">
         <v>8721.555</v>
       </c>
       <c r="H36" s="55">
@@ -1647,7 +1647,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" ht="33" customHeight="1" s="50">
+    <row r="37" ht="49.5" customHeight="1" s="50">
       <c r="B37" s="56" t="n"/>
       <c r="C37" s="48" t="inlineStr">
         <is>
@@ -1661,13 +1661,13 @@
 ※ 12월 말까지 집행 완료</t>
         </is>
       </c>
-      <c r="E37" s="65" t="n">
+      <c r="E37" s="78" t="n">
         <v>1463</v>
       </c>
-      <c r="F37" s="65" t="n">
+      <c r="F37" s="78" t="n">
         <v>0</v>
       </c>
-      <c r="G37" s="66" t="n">
+      <c r="G37" s="79" t="n">
         <v>1463</v>
       </c>
       <c r="H37" s="55">
@@ -1679,7 +1679,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" ht="66" customHeight="1" s="50">
+    <row r="38" ht="64" customHeight="1" s="50">
       <c r="B38" s="56" t="n"/>
       <c r="C38" s="48" t="inlineStr">
         <is>
@@ -1693,13 +1693,13 @@
 ※ 12월 말까지 집행 완료</t>
         </is>
       </c>
-      <c r="E38" s="67" t="n">
+      <c r="E38" s="80" t="n">
         <v>7836</v>
       </c>
-      <c r="F38" s="67" t="n">
+      <c r="F38" s="80" t="n">
         <v>3918</v>
       </c>
-      <c r="G38" s="66" t="n">
+      <c r="G38" s="79" t="n">
         <v>3918</v>
       </c>
       <c r="H38" s="55">
@@ -1711,7 +1711,7 @@
         <v/>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="20.5" customHeight="1" s="50">
       <c r="B39" s="56" t="n"/>
       <c r="C39" s="48" t="inlineStr">
         <is>
@@ -1723,13 +1723,13 @@
           <t>해당 없음</t>
         </is>
       </c>
-      <c r="E39" s="65" t="n">
+      <c r="E39" s="78" t="n">
         <v>0</v>
       </c>
-      <c r="F39" s="65" t="n">
+      <c r="F39" s="78" t="n">
         <v>0</v>
       </c>
-      <c r="G39" s="66" t="n">
+      <c r="G39" s="79" t="n">
         <v>0</v>
       </c>
       <c r="H39" s="55">
@@ -1741,7 +1741,7 @@
         <v/>
       </c>
     </row>
-    <row r="40">
+    <row r="40" ht="20.5" customHeight="1" s="50">
       <c r="B40" s="56" t="n"/>
       <c r="C40" s="48" t="inlineStr">
         <is>
@@ -1753,13 +1753,13 @@
           <t>해당 없음</t>
         </is>
       </c>
-      <c r="E40" s="65" t="n">
+      <c r="E40" s="78" t="n">
         <v>0</v>
       </c>
-      <c r="F40" s="65" t="n">
+      <c r="F40" s="78" t="n">
         <v>0</v>
       </c>
-      <c r="G40" s="66" t="n">
+      <c r="G40" s="79" t="n">
         <v>0</v>
       </c>
       <c r="H40" s="55">
@@ -1771,7 +1771,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" ht="115" customHeight="1" s="50">
+    <row r="41" ht="180" customHeight="1" s="50">
       <c r="B41" s="56" t="n"/>
       <c r="C41" s="48" t="inlineStr">
         <is>
@@ -1789,13 +1789,13 @@
    - 실증 측정장비 구입: HBP 침상·우사 환경 측정용 4,500천원(11월 초) — 휴대용 암모니아 측정기, 침상 수분계, 탐침 온도계, pH 측정기, 온습도 데이터로거, 거리·깊이 측정 도구, 교정액·소모품</t>
         </is>
       </c>
-      <c r="E41" s="67" t="n">
+      <c r="E41" s="80" t="n">
         <v>32164</v>
       </c>
-      <c r="F41" s="67" t="n">
+      <c r="F41" s="80" t="n">
         <v>0</v>
       </c>
-      <c r="G41" s="66" t="n">
+      <c r="G41" s="79" t="n">
         <v>32164</v>
       </c>
       <c r="H41" s="55">
@@ -1807,7 +1807,7 @@
         <v/>
       </c>
     </row>
-    <row r="42">
+    <row r="42" ht="20.5" customHeight="1" s="50">
       <c r="B42" s="59" t="n"/>
       <c r="C42" s="48" t="inlineStr">
         <is>
@@ -1819,13 +1819,13 @@
           <t>해당 없음</t>
         </is>
       </c>
-      <c r="E42" s="65" t="n">
+      <c r="E42" s="78" t="n">
         <v>0</v>
       </c>
-      <c r="F42" s="65" t="n">
+      <c r="F42" s="78" t="n">
         <v>0</v>
       </c>
-      <c r="G42" s="66" t="n">
+      <c r="G42" s="79" t="n">
         <v>0</v>
       </c>
       <c r="H42" s="55">
@@ -1837,7 +1837,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" ht="33" customHeight="1" s="50">
+    <row r="43" ht="35" customHeight="1" s="50">
       <c r="B43" s="48" t="inlineStr">
         <is>
           <t>간접비</t>
@@ -1854,13 +1854,13 @@
 ※ 12월 말까지 집행 완료</t>
         </is>
       </c>
-      <c r="E43" s="65" t="n">
+      <c r="E43" s="78" t="n">
         <v>2000</v>
       </c>
-      <c r="F43" s="65" t="n">
+      <c r="F43" s="78" t="n">
         <v>0</v>
       </c>
-      <c r="G43" s="66" t="n">
+      <c r="G43" s="79" t="n">
         <v>2000</v>
       </c>
       <c r="H43" s="55">
@@ -1880,15 +1880,15 @@
       </c>
       <c r="C44" s="60" t="n"/>
       <c r="D44" s="61" t="n"/>
-      <c r="E44" s="62">
+      <c r="E44" s="81">
         <f>SUM(E36:E43)</f>
         <v/>
       </c>
-      <c r="F44" s="62">
+      <c r="F44" s="81">
         <f>SUM(F36:F43)</f>
         <v/>
       </c>
-      <c r="G44" s="63">
+      <c r="G44" s="82">
         <f>SUM(G36:G43)</f>
         <v/>
       </c>
@@ -1916,6 +1916,10 @@
     <mergeCell ref="B8:C8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="32" min="0" max="16383" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>
 
@@ -1923,7 +1927,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
@@ -2322,5 +2326,6 @@
     <mergeCell ref="B17:C17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>